--- a/03APRIL.xlsx
+++ b/03APRIL.xlsx
@@ -490,7 +490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -694,6 +694,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -7187,7 +7188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="67" min="1" max="1"/>
@@ -7278,6 +7279,66 @@
       <c r="E4" s="73" t="inlineStr">
         <is>
           <t>ILLUSTRATIVE EXAMPLE: 60,000 SGD/year ≈ 12% of CAPEX per year. Typical OPEX/CAPEX ratio for industrial recycling facilities: 10–20% per year (Ecocycle 2021; various IS hub feasibility studies). Does NOT include variable storage OPEX (read from Intermediate sheet B8). Replace with actual operating cost estimates before submitting results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>brickYield_tPerTAsh</t>
+        </is>
+      </c>
+      <c r="B5" s="79" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>t bricks / t bottom ash</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>~300-400 bricks per tonne ash at 2-3 kg/brick. Default 0.30 [ILLUSTRATIVE]. xxx: replace with BIWASE operational data before submission. Source: [TRAINING]. AnyLogic reads: getCellNumericValue('Intermediate Investment', 5, 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>brickPrice_SGD_t</t>
+        </is>
+      </c>
+      <c r="B6" s="79" t="n">
+        <v>150</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SGD / tonne bricks</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Market price for BIWASE ash-fired bricks. Vietnamese hollow brick ~30-50 USD/t. Default 150 SGD/t [ILLUSTRATIVE]. xxx: replace with BIWASE market price before submission. [TRAINING]. AnyLogic reads: getCellNumericValue('Intermediate Investment', 6, 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>brickPlantCapex_SGD</t>
+        </is>
+      </c>
+      <c r="B7" s="79" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Brick kiln CAPEX. ESCAR p.70: tunnel kiln 100,000 bricks/day capacity. Vietnam tunnel kiln ~300k-1M USD. Default 500,000 SGD [ILLUSTRATIVE]. Deducted at t=0 with storage + recycling plant CAPEX. xxx: replace with actual BIWASE capital cost before submission. [TRAINING]. AnyLogic reads: getCellNumericValue('Intermediate Investment', 7, 2)</t>
         </is>
       </c>
     </row>
@@ -9985,8 +10046,8 @@
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="A15:A17"/>
+    <mergeCell ref="B3:B5"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="B3:B5"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="A18:A20"/>
   </mergeCells>
@@ -10412,7 +10473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col width="28" customWidth="1" style="67" min="1" max="1"/>
@@ -11121,6 +11182,33 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>Graedel et al. 2011; Daigo et al. 2017; VASMA [GREY] [ASSUMED]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>── MSW 50/50 incineration/landfill split ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>msw_incinerationFrac_of_49pct</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>xxx: MODELING ASSUMPTION — 50% of MSW non-recyclable fraction (49.5%) goes to incineration, 50% to landfill. Subject to sensitivity analysis. No ESCAR data for this split. BIWASE WtE capacity 201.6 tpd vs ~2990 tpd MSW received → WtE can only handle ~6.7% of total. Assumption needs calibration before thesis submission. [ASSUMED]</t>
         </is>
       </c>
     </row>

--- a/03APRIL.xlsx
+++ b/03APRIL.xlsx
@@ -490,7 +490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -695,6 +695,10 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1031,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U75"/>
+  <dimension ref="A1:U76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col width="6" customWidth="1" style="67" min="1" max="1"/>
@@ -6979,188 +6983,249 @@
       <c r="U72" s="4" t="n"/>
     </row>
     <row r="73" ht="18" customHeight="1" s="67">
-      <c r="A73" s="6" t="n"/>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="A73" t="n">
+        <v>6</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Receiver_Organic_Agri</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Receiver</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ORGANIC_WASTE</t>
+        </is>
+      </c>
+      <c r="E73" s="80" t="n">
+        <v>10.945</v>
+      </c>
+      <c r="F73" s="80" t="n">
+        <v>106.71</v>
+      </c>
+      <c r="G73" s="80" t="n">
+        <v>8</v>
+      </c>
+      <c r="H73" s="80" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Crop and animal production</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Agricultural cooperative or fertiliser distributor. Receives compost from BIWASE composting facility as soil amendment for Binh Duong region farms. IS pathway: organic waste → composting → compost product → agricultural Receiver.</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>ORGANIC_WASTE (compost buyer)</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Binh Duong Province, Vietnam (representative agricultural node) [ILLUSTRATIVE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1" s="67">
+      <c r="A74" s="6" t="n"/>
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>VSIP1 Recycling Intermediate</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>Intermediate</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E73" s="40" t="n">
+      <c r="E74" s="40" t="n">
         <v>10.93</v>
       </c>
-      <c r="F73" s="40" t="n">
+      <c r="F74" s="40" t="n">
         <v>106.72</v>
       </c>
-      <c r="G73" s="6" t="n"/>
-      <c r="H73" s="6" t="n">
+      <c r="G74" s="6" t="n"/>
+      <c r="H74" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="J73" s="6" t="n"/>
-      <c r="K73" s="6" t="n"/>
-      <c r="L73" s="6" t="n"/>
-      <c r="M73" s="6" t="inlineStr">
+      <c r="J74" s="6" t="n"/>
+      <c r="K74" s="6" t="n"/>
+      <c r="L74" s="6" t="n"/>
+      <c r="M74" s="6" t="inlineStr">
         <is>
           <t>Central recycling hub</t>
         </is>
       </c>
-      <c r="N73" s="6" t="n"/>
-      <c r="O73" s="6" t="n"/>
-      <c r="P73" s="6" t="n"/>
-      <c r="Q73" s="6" t="inlineStr">
+      <c r="N74" s="6" t="n"/>
+      <c r="O74" s="6" t="n"/>
+      <c r="P74" s="6" t="n"/>
+      <c r="Q74" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R73" s="6" t="inlineStr">
+      <c r="R74" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S73" s="6" t="inlineStr">
+      <c r="S74" s="6" t="inlineStr">
         <is>
           <t>Model assumption (central hub location)</t>
         </is>
       </c>
-      <c r="T73" s="7" t="n"/>
-      <c r="U73" s="7" t="n"/>
-    </row>
-    <row r="74" ht="18" customHeight="1" s="67">
-      <c r="A74" s="2" t="n"/>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="T74" s="7" t="n"/>
+      <c r="U74" s="7" t="n"/>
+    </row>
+    <row r="75" ht="18" customHeight="1" s="67">
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Da Phuoc Landfill</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>EndOfLife</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E75" s="2" t="n">
         <v>10.665415</v>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="F75" s="2" t="n">
         <v>106.665886</v>
       </c>
-      <c r="G74" s="2" t="n"/>
-      <c r="H74" s="2" t="n">
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="J74" s="2" t="n"/>
-      <c r="K74" s="2" t="n"/>
-      <c r="L74" s="2" t="n"/>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="J75" s="2" t="n"/>
+      <c r="K75" s="2" t="n"/>
+      <c r="L75" s="2" t="n"/>
+      <c r="M75" s="2" t="inlineStr">
         <is>
           <t>[SUPERSEDED — not used in CE 3.0 model] Municipal solid waste landfill. Replaced by BIWASE ETS (row 90) as the industrial waste EndOfLife agent. Da Phuoc is a municipal landfill (HCM City) and is not appropriate for industrial IS network modelling in Binh Duong.</t>
         </is>
       </c>
-      <c r="N74" s="2" t="n"/>
-      <c r="O74" s="2" t="inlineStr">
+      <c r="N75" s="2" t="n"/>
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t>Phước Hiệp, Bình Chánh, HCMC</t>
         </is>
       </c>
-      <c r="P74" s="2" t="n"/>
-      <c r="Q74" s="2" t="inlineStr">
+      <c r="P75" s="2" t="n"/>
+      <c r="Q75" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R74" s="2" t="inlineStr">
+      <c r="R75" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S74" s="2" t="inlineStr">
+      <c r="S75" s="2" t="inlineStr">
         <is>
           <t>Finneiss DB (Landfills_Location); https://www.researchgate.net/publication/356037309_Research_on_appropriate_technology_solutions_for_the_treatment_of_leachate_in_Phuoc_Hiep_landfill_in_Ho_Chi_Minh_City | NOTE: Row superseded by BIWASE ETS (row 90) in CE 3.0. Da Phuoc is municipal, not industrial. See: Materials marketplace final report PDF.</t>
         </is>
       </c>
-      <c r="T74" s="2" t="n">
+      <c r="T75" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="U74" s="2" t="inlineStr">
+      <c r="U75" s="2" t="inlineStr">
         <is>
           <t>SGD/t</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1" s="67">
-      <c r="A75" s="7" t="n"/>
-      <c r="B75" s="7" t="inlineStr">
+    <row r="76" ht="18" customHeight="1" s="67">
+      <c r="A76" s="7" t="n"/>
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">BIWASE ETS Waste Treatment Complex </t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>EndOfLife</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E76" s="5" t="n">
         <v>11.085</v>
       </c>
-      <c r="F75" s="8" t="n">
+      <c r="F76" s="8" t="n">
         <v>106.59</v>
       </c>
-      <c r="G75" s="7" t="n"/>
-      <c r="H75" s="7" t="n">
+      <c r="G76" s="7" t="n"/>
+      <c r="H76" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="J75" s="7" t="n"/>
-      <c r="K75" s="7" t="n"/>
-      <c r="L75" s="7" t="n"/>
-      <c r="M75" s="7" t="inlineStr">
+      <c r="J76" s="7" t="n"/>
+      <c r="K76" s="7" t="n"/>
+      <c r="L76" s="7" t="n"/>
+      <c r="M76" s="7" t="inlineStr">
         <is>
           <t>Industrial and hazardous waste treatment complex. Handles mixed industrial, chemical, and solid waste from Binh Duong province. Operations include sanitary landfilling, composting, and waste-to-energy (WtE) incineration. Designated industrial EndOfLife agent for CE 3.0 model at VSIP1.</t>
         </is>
       </c>
-      <c r="N75" s="7" t="n"/>
-      <c r="O75" s="9" t="inlineStr">
+      <c r="N76" s="7" t="n"/>
+      <c r="O76" s="9" t="inlineStr">
         <is>
           <t>No. 39, Group 8, Quarter 1B, Chanh Phu Hoa Ward, Ben Cat City, Binh Duong Province, Vietnam</t>
         </is>
       </c>
-      <c r="P75" s="7" t="n"/>
-      <c r="Q75" s="7" t="inlineStr">
+      <c r="P76" s="7" t="n"/>
+      <c r="Q76" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R75" s="7" t="inlineStr">
+      <c r="R76" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S75" s="7" t="inlineStr">
+      <c r="S76" s="7" t="inlineStr">
         <is>
           <t>Materials marketplace final report PDF. Location confirmed: No. 39, Group 8, Quarter 1B, Chanh Phu Hoa Ward, Ben Cat City, Binh Duong Province, Vietnam. Designated industrial/hazardous waste treatment facility for Binh Duong province; replaces Da Phuoc (municipal landfill) as EndOfLife agent in CE 3.0 model.</t>
         </is>
       </c>
-      <c r="T75" s="7" t="n"/>
-      <c r="U75" s="7" t="n"/>
-    </row>
-    <row r="76" ht="18" customHeight="1" s="67"/>
+      <c r="T76" s="7" t="n"/>
+      <c r="U76" s="7" t="n"/>
+    </row>
     <row r="77" ht="18" customHeight="1" s="67"/>
     <row r="78" ht="18" customHeight="1" s="67"/>
     <row r="79" ht="18" customHeight="1" s="67"/>
@@ -7356,7 +7421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col width="20" customWidth="1" style="67" min="1" max="1"/>
@@ -7870,6 +7935,81 @@
         <v>20</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ORGANIC_WASTE</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C8" s="37" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D8" s="37" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E8" s="37" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F8" s="37" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G8" s="37" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H8" s="37" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I8" s="37" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J8" s="37" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="K8" s="37" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="L8" s="37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M8" s="37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N8" s="37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O8" s="37" t="n">
+        <v>50</v>
+      </c>
+      <c r="P8" s="37" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q8" s="37" t="n">
+        <v>20</v>
+      </c>
+      <c r="R8" t="n">
+        <v>60</v>
+      </c>
+      <c r="S8">
+        <f>R8*1.35</f>
+        <v/>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>ESCAR (2019) BIWASE composting facility, Binh Duong; compost price proxy SE Asia market [ILLUSTRATIVE]</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>ConversionEff 20%: 5:1 organic waste to compost (ESCAR pp.34-39). GWP_Composting 0.055 kg CO2-eq/kg: ecoinvent 3.9 biowaste composting proxy [ILLUSTRATIVE]. GWP_Landfill 0.52: CH4 biogenic fraction from organic waste landfill [ILLUSTRATIVE]. compostPrice 80 SGD/t = 60 USD/t: SE Asia compost market proxy. All LCA factors [ILLUSTRATIVE] — must be replaced with ecoinvent 3.9 values from CE30_EcoinventSearchStrings.md section E.</t>
+        </is>
+      </c>
+      <c r="V8" s="37" t="n">
+        <v>-5</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
@@ -7885,7 +8025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="18" customWidth="1" style="67" min="1" max="1"/>
@@ -8365,6 +8505,56 @@
       <c r="H13" s="36" t="inlineStr">
         <is>
           <t>High-value metal residue; returned to Intermediate. Intermediate pays Provider for this stream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="81" t="inlineStr">
+        <is>
+          <t>ORGANIC_WASTE</t>
+        </is>
+      </c>
+      <c r="B14" s="81" t="inlineStr">
+        <is>
+          <t>Conversion Efficiency (Composting)</t>
+        </is>
+      </c>
+      <c r="C14" s="82" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D14" s="81" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="E14" s="81" t="inlineStr">
+        <is>
+          <t>conversionEffPerMat[5]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="83" t="inlineStr">
+        <is>
+          <t>ORGANIC_WASTE</t>
+        </is>
+      </c>
+      <c r="B15" s="83" t="inlineStr">
+        <is>
+          <t>processingEfficiency (ORGANIC_WASTE)</t>
+        </is>
+      </c>
+      <c r="C15" s="82" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D15" s="83" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="E15" s="83" t="inlineStr">
+        <is>
+          <t>processingEffPerMat[5]</t>
         </is>
       </c>
     </row>
@@ -10046,8 +10236,8 @@
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="B3:B5"/>
-    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="A18:A20"/>
   </mergeCells>
